--- a/termine.xlsx
+++ b/termine.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDB4432-D235-3748-AA23-2923D86B744F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Datum</t>
   </si>
@@ -79,6 +79,15 @@
   </si>
   <si>
     <t>Martinimarkt</t>
+  </si>
+  <si>
+    <t>19 Uhr, 18 Uhr Einlass</t>
+  </si>
+  <si>
+    <t>Sankt Augustin</t>
+  </si>
+  <si>
+    <t>Schützenhaus Hangelar</t>
   </si>
 </sst>
 </file>
@@ -86,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -128,10 +137,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -434,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.98828125" customWidth="1"/>
@@ -531,6 +541,20 @@
         <v>16</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>46424</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/termine.xlsx
+++ b/termine.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDB4432-D235-3748-AA23-2923D86B744F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECB5BB02-D1CF-2747-AEC8-FC1C4C1E9B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Datum</t>
   </si>
@@ -81,13 +81,16 @@
     <t>Martinimarkt</t>
   </si>
   <si>
-    <t>19 Uhr, 18 Uhr Einlass</t>
-  </si>
-  <si>
     <t>Sankt Augustin</t>
   </si>
   <si>
     <t>Schützenhaus Hangelar</t>
+  </si>
+  <si>
+    <t>19 Uhr</t>
+  </si>
+  <si>
+    <t>Mitsing-Party</t>
   </si>
 </sst>
 </file>
@@ -546,13 +549,16 @@
         <v>46424</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>19</v>
+      <c r="E7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
